--- a/groupe_surfaces_and_volumes.xlsx
+++ b/groupe_surfaces_and_volumes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emil\Desktop\Msc Thesis\UNIFAC_DORTMUND\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/bjemli_dtu_dk/Documents/Skrivebord/snake stuff/UNIFAC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579C3C62-FA67-4DAE-B120-BA7F044804FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{579C3C62-FA67-4DAE-B120-BA7F044804FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8181F8AD-404C-4C0D-BB87-331730016401}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F7FF660B-5B5E-499A-B5D6-49A9A79AF277}"/>
+    <workbookView xWindow="-28920" yWindow="525" windowWidth="29040" windowHeight="17520" xr2:uid="{F7FF660B-5B5E-499A-B5D6-49A9A79AF277}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -866,10 +866,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAFC05B3-0F03-4247-A327-7E6604775786}">
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -889,7 +889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -908,8 +908,9 @@
       <c r="F2" s="1">
         <v>1.0608</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -928,8 +929,9 @@
       <c r="F3" s="1">
         <v>0.70809999999999995</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -948,8 +950,9 @@
       <c r="F4" s="1">
         <v>0.35539999999999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -968,8 +971,9 @@
       <c r="F5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -988,8 +992,9 @@
       <c r="F6" s="1">
         <v>1.6015999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1008,8 +1013,9 @@
       <c r="F7" s="1">
         <v>1.2488999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1029,7 +1035,7 @@
         <v>1.2488999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1049,7 +1055,7 @@
         <v>0.8962</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1069,7 +1075,7 @@
         <v>0.43209999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1089,7 +1095,7 @@
         <v>0.21129999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1109,7 +1115,7 @@
         <v>0.94899999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1129,7 +1135,7 @@
         <v>0.79620000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1149,7 +1155,7 @@
         <v>0.37690000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1169,7 +1175,7 @@
         <v>0.89270000000000005</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
